--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.77706</v>
+        <v>16.9319</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49793</v>
+        <v>16.43153</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82325</v>
+        <v>16.82418</v>
       </c>
       <c r="F2" t="n">
-        <v>42.34785</v>
+        <v>41.99188</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04973</v>
+        <v>0.05005</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7913</v>
+        <v>1.82056</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.67532</v>
+        <v>17.00862</v>
       </c>
       <c r="D3" t="n">
-        <v>16.29519</v>
+        <v>15.99296</v>
       </c>
       <c r="E3" t="n">
-        <v>16.76393</v>
+        <v>16.62458</v>
       </c>
       <c r="F3" t="n">
-        <v>42.72854</v>
+        <v>42.66432</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05026</v>
+        <v>0.05007</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80986</v>
+        <v>1.80506</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.79789</v>
+        <v>16.78407</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59364</v>
+        <v>16.32258</v>
       </c>
       <c r="E4" t="n">
-        <v>16.28436</v>
+        <v>16.60575</v>
       </c>
       <c r="F4" t="n">
-        <v>42.23442</v>
+        <v>42.61478</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0498</v>
+        <v>0.05078</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79372</v>
+        <v>1.82121</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.47158</v>
+        <v>16.71518</v>
       </c>
       <c r="D6" t="n">
-        <v>15.94866</v>
+        <v>15.77737</v>
       </c>
       <c r="E6" t="n">
-        <v>16.37112</v>
+        <v>16.51132</v>
       </c>
       <c r="F6" t="n">
-        <v>22.29104</v>
+        <v>21.63253</v>
       </c>
       <c r="G6" t="n">
-        <v>34.41541</v>
+        <v>34.10266</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.50502</v>
+        <v>16.69682</v>
       </c>
       <c r="D7" t="n">
-        <v>16.08803</v>
+        <v>15.70605</v>
       </c>
       <c r="E7" t="n">
-        <v>16.25944</v>
+        <v>16.57892</v>
       </c>
       <c r="F7" t="n">
-        <v>21.44882</v>
+        <v>21.65675</v>
       </c>
       <c r="G7" t="n">
-        <v>34.27554</v>
+        <v>33.55843</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.22787</v>
+        <v>17.11553</v>
       </c>
       <c r="D8" t="n">
-        <v>16.05104</v>
+        <v>15.91699</v>
       </c>
       <c r="E8" t="n">
-        <v>16.07159</v>
+        <v>16.04343</v>
       </c>
       <c r="F8" t="n">
-        <v>21.51111</v>
+        <v>21.60495</v>
       </c>
       <c r="G8" t="n">
-        <v>34.27114</v>
+        <v>34.59868</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60249</v>
+        <v>0.60603</v>
       </c>
       <c r="D10" t="n">
-        <v>1.141</v>
+        <v>1.11574</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60348</v>
+        <v>0.59856</v>
       </c>
       <c r="D11" t="n">
-        <v>1.117</v>
+        <v>1.11462</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59467</v>
+        <v>0.60556</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1032</v>
+        <v>1.10236</v>
       </c>
     </row>
   </sheetData>
